--- a/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Qwen3-Next-80B-A3B-Instruct/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Qwen3-Next-80B-A3B-Instruct/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>385</v>
+        <v>398</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>337</v>
+        <v>408</v>
       </c>
       <c r="D3">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E3">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>53</v>
+        <v>3</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Qwen3-Next-80B-A3B-Instruct/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Qwen3-Next-80B-A3B-Instruct/default/total_votes_file.xlsx
@@ -433,13 +433,13 @@
         <v>398</v>
       </c>
       <c r="D2">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H3">
         <v>426</v>
